--- a/events/Vaires_2024_OG/Vaires_2024_OG_start.xlsx
+++ b/events/Vaires_2024_OG/Vaires_2024_OG_start.xlsx
@@ -37920,10 +37920,10 @@
         <v>464</v>
       </c>
       <c r="M623" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N623" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R623" t="inlineStr">
         <is>
@@ -37989,10 +37989,10 @@
         <v>464</v>
       </c>
       <c r="M624" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N624" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R624" t="inlineStr">
         <is>
@@ -38058,10 +38058,10 @@
         <v>464</v>
       </c>
       <c r="M625" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N625" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R625" t="inlineStr">
         <is>
@@ -38127,10 +38127,10 @@
         <v>464</v>
       </c>
       <c r="M626" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N626" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R626" t="inlineStr">
         <is>
@@ -38196,10 +38196,10 @@
         <v>465</v>
       </c>
       <c r="M627" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N627" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R627" t="inlineStr">
         <is>
@@ -38265,10 +38265,10 @@
         <v>465</v>
       </c>
       <c r="M628" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N628" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R628" t="inlineStr">
         <is>
@@ -38334,10 +38334,10 @@
         <v>465</v>
       </c>
       <c r="M629" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N629" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R629" t="inlineStr">
         <is>
@@ -38403,10 +38403,10 @@
         <v>465</v>
       </c>
       <c r="M630" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N630" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R630" t="inlineStr">
         <is>

--- a/events/Vaires_2024_OG/Vaires_2024_OG_start.xlsx
+++ b/events/Vaires_2024_OG/Vaires_2024_OG_start.xlsx
@@ -37895,7 +37895,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -37964,7 +37964,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -38033,7 +38033,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -38102,7 +38102,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -38171,7 +38171,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -38240,7 +38240,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -38309,7 +38309,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -38378,7 +38378,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
